--- a/cet4/result/13_重生学霸_清华北大的女神之路/13_重生学霸_清华北大的女神之路_学习版.xlsx
+++ b/cet4/result/13_重生学霸_清华北大的女神之路/13_重生学霸_清华北大的女神之路_学习版.xlsx
@@ -397,1011 +397,787 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D55"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>youth</v>
       </c>
       <c r="B2" t="str">
-        <v>youth</v>
+        <v>/juːθ/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>青年</v>
       </c>
-      <c r="D2" t="str">
-        <v>youth(青年)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>boy</v>
       </c>
       <c r="B3" t="str">
-        <v>boy</v>
+        <v>/bɔɪ/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>男孩</v>
       </c>
-      <c r="D3" t="str">
-        <v>boy(男孩)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>essential</v>
       </c>
       <c r="B4" t="str">
-        <v>essential</v>
+        <v>/ɪˈsenʃl/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>基本的</v>
       </c>
-      <c r="D4" t="str">
-        <v>essential(基本的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>northeast</v>
       </c>
       <c r="B5" t="str">
-        <v>northeast</v>
+        <v>/ˌnɔːrθˈiːst/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>东北</v>
       </c>
-      <c r="D5" t="str">
-        <v>northeast(东北)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>fertile</v>
       </c>
       <c r="B6" t="str">
-        <v>fertile</v>
+        <v>/ˈfɜːrtl/</v>
       </c>
       <c r="C6" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>肥沃的</v>
       </c>
-      <c r="D6" t="str">
-        <v>fertile(肥沃的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>throng</v>
       </c>
       <c r="B7" t="str">
-        <v>throng</v>
+        <v>/θrɔːŋ/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>人群</v>
       </c>
-      <c r="D7" t="str">
-        <v>throng(人群)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>steady</v>
       </c>
       <c r="B8" t="str">
-        <v>steady</v>
+        <v>/ˈstedi/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D8" t="str">
         <v>稳固的</v>
       </c>
-      <c r="D8" t="str">
-        <v>steady(稳固的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>yard</v>
       </c>
       <c r="B9" t="str">
-        <v>yard</v>
+        <v>/jɑːrd/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D9" t="str">
         <v>庭院</v>
       </c>
-      <c r="D9" t="str">
-        <v>yard(庭院)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>western</v>
       </c>
       <c r="B10" t="str">
-        <v>western</v>
+        <v>/ˈwestərn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>西部</v>
       </c>
-      <c r="D10" t="str">
-        <v>western(西部)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>sore</v>
       </c>
       <c r="B11" t="str">
-        <v>sore</v>
+        <v>/sɔːr/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>疼痛的</v>
       </c>
-      <c r="D11" t="str">
-        <v>sore(疼痛的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>optimistic</v>
       </c>
       <c r="B12" t="str">
-        <v>optimistic</v>
+        <v>/ˌɑːptɪˈmɪstɪk/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>乐观的</v>
       </c>
-      <c r="D12" t="str">
-        <v>optimistic(乐观的)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>structure</v>
       </c>
       <c r="B13" t="str">
-        <v>structure</v>
+        <v>/ˈstrʌktʃər/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D13" t="str">
         <v>结构</v>
       </c>
-      <c r="D13" t="str">
-        <v>structure(结构)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>shop</v>
       </c>
       <c r="B14" t="str">
-        <v>shop</v>
+        <v>/ʃɑːp/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D14" t="str">
         <v>商店</v>
       </c>
-      <c r="D14" t="str">
-        <v>shop(商店)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>Western</v>
       </c>
       <c r="B15" t="str">
-        <v>Western</v>
+        <v/>
       </c>
       <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
         <v>西式</v>
       </c>
-      <c r="D15" t="str">
-        <v>Western(西式)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>pie</v>
       </c>
       <c r="B16" t="str">
-        <v>pie</v>
+        <v>/paɪ/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D16" t="str">
         <v>馅饼</v>
       </c>
-      <c r="D16" t="str">
-        <v>pie(馅饼)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>weak</v>
       </c>
       <c r="B17" t="str">
-        <v>weak</v>
+        <v>/wiːk/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>软的</v>
       </c>
-      <c r="D17" t="str">
-        <v>weak(软的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>potato</v>
       </c>
       <c r="B18" t="str">
-        <v>potato</v>
+        <v>/pəˈteɪtoʊ/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>土豆</v>
       </c>
-      <c r="D18" t="str">
-        <v>potato(土豆)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>success</v>
       </c>
       <c r="B19" t="str">
-        <v>success</v>
+        <v>/səkˈses/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>成功</v>
       </c>
-      <c r="D19" t="str">
-        <v>success(成功)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>Roman</v>
       </c>
       <c r="B20" t="str">
-        <v>Roman</v>
+        <v>/ˈroʊmən/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>罗马</v>
       </c>
-      <c r="D20" t="str">
-        <v>Roman(罗马)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>collect</v>
       </c>
       <c r="B21" t="str">
-        <v>collect</v>
+        <v>/kəˈlekt/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D21" t="str">
         <v>收集</v>
       </c>
-      <c r="D21" t="str">
-        <v>collect(收集)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>heap</v>
       </c>
       <c r="B22" t="str">
-        <v>heap</v>
+        <v>/hiːp/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>堆</v>
       </c>
-      <c r="D22" t="str">
-        <v>heap(堆)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>alike</v>
       </c>
       <c r="B23" t="str">
-        <v>alike</v>
+        <v>/əˈlaɪk/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D23" t="str">
         <v>相似的</v>
       </c>
-      <c r="D23" t="str">
-        <v>alike(相似的)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>word</v>
       </c>
       <c r="B24" t="str">
-        <v>word</v>
+        <v>/wɜːrd/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D24" t="str">
         <v>词语</v>
       </c>
-      <c r="D24" t="str">
-        <v>word(词语)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>burden</v>
       </c>
       <c r="B25" t="str">
-        <v>burden</v>
+        <v>/ˈbɜːrdn/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D25" t="str">
         <v>负担</v>
       </c>
-      <c r="D25" t="str">
-        <v>burden(负担)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>disaster</v>
       </c>
       <c r="B26" t="str">
-        <v>disaster</v>
+        <v>/dɪˈzæstər/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>灾难</v>
       </c>
-      <c r="D26" t="str">
-        <v>disaster(灾难)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>ill</v>
       </c>
       <c r="B27" t="str">
-        <v>ill</v>
+        <v>/ɪl/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D27" t="str">
         <v>生病</v>
       </c>
-      <c r="D27" t="str">
-        <v>ill(生病)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>continue</v>
       </c>
       <c r="B28" t="str">
-        <v>weak</v>
+        <v>/kənˈtɪnjuː/</v>
       </c>
       <c r="C28" t="str">
-        <v>虚弱</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>weak(虚弱)📢</v>
+        <v>继续</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>reputation</v>
       </c>
       <c r="B29" t="str">
-        <v>continue</v>
+        <v>/ˌrepjuˈteɪʃn/</v>
       </c>
       <c r="C29" t="str">
-        <v>继续</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>continue(继续)📢</v>
+        <v>声誉</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>noticeable</v>
       </c>
       <c r="B30" t="str">
-        <v>reputation</v>
+        <v>/ˈnoʊtɪsəbl/</v>
       </c>
       <c r="C30" t="str">
-        <v>声誉</v>
+        <v>adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>reputation(声誉)📢</v>
+        <v>显著的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>mine</v>
       </c>
       <c r="B31" t="str">
-        <v>noticeable</v>
+        <v>/maɪn/</v>
       </c>
       <c r="C31" t="str">
-        <v>显著的</v>
+        <v>n./vt./vi./pron.</v>
       </c>
       <c r="D31" t="str">
-        <v>noticeable(显著的)📢</v>
+        <v>矿</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>gardener</v>
       </c>
       <c r="B32" t="str">
-        <v>mine</v>
+        <v>/ˈɡɑːrdnər/</v>
       </c>
       <c r="C32" t="str">
-        <v>矿</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>mine(矿)📢</v>
+        <v>园丁</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>civilization</v>
       </c>
       <c r="B33" t="str">
-        <v>gardener</v>
+        <v>/ˌsɪvələˈzeɪʃn/</v>
       </c>
       <c r="C33" t="str">
-        <v>园丁</v>
+        <v>n.</v>
       </c>
       <c r="D33" t="str">
-        <v>gardener(园丁)📢</v>
+        <v>文明</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>observation</v>
       </c>
       <c r="B34" t="str">
-        <v>Roman</v>
+        <v>/ˌɑːbzərˈveɪʃn/</v>
       </c>
       <c r="C34" t="str">
-        <v>罗马</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>Roman(罗马)📢</v>
+        <v>观察</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>fibre</v>
       </c>
       <c r="B35" t="str">
-        <v>civilization</v>
+        <v>/ˈfaɪbər/</v>
       </c>
       <c r="C35" t="str">
-        <v>文明</v>
+        <v>n.</v>
       </c>
       <c r="D35" t="str">
-        <v>civilization(文明)📢</v>
+        <v>纤维</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>rigid</v>
       </c>
       <c r="B36" t="str">
-        <v>observation</v>
+        <v>/ˈrɪdʒɪd/</v>
       </c>
       <c r="C36" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>刻板的</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>care</v>
+      </c>
+      <c r="B37" t="str">
+        <v>/ker/</v>
+      </c>
+      <c r="C37" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D37" t="str">
+        <v>关注</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>drive</v>
+      </c>
+      <c r="B38" t="str">
+        <v>/draɪv/</v>
+      </c>
+      <c r="C38" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D38" t="str">
+        <v>驱动</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>stripe</v>
+      </c>
+      <c r="B39" t="str">
+        <v>/straɪp/</v>
+      </c>
+      <c r="C39" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D39" t="str">
+        <v>条纹</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>invade</v>
+      </c>
+      <c r="B40" t="str">
+        <v>/ɪnˈveɪd/</v>
+      </c>
+      <c r="C40" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D40" t="str">
+        <v>进入</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>aboard</v>
+      </c>
+      <c r="B41" t="str">
+        <v>/əˈbɔːrd/</v>
+      </c>
+      <c r="C41" t="str">
+        <v>v./adv./prep.</v>
+      </c>
+      <c r="D41" t="str">
+        <v>在车上</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>instance</v>
+      </c>
+      <c r="B42" t="str">
+        <v>/ˈɪnstəns/</v>
+      </c>
+      <c r="C42" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D42" t="str">
+        <v>例子</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>lavatory</v>
+      </c>
+      <c r="B43" t="str">
+        <v>/ˈlævətɔːri/</v>
+      </c>
+      <c r="C43" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D43" t="str">
+        <v>厕所</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>dot</v>
+      </c>
+      <c r="B44" t="str">
+        <v>/dɑːt/</v>
+      </c>
+      <c r="C44" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D44" t="str">
+        <v>小点</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>license</v>
+      </c>
+      <c r="B45" t="str">
+        <v>/ˈlaɪsns/</v>
+      </c>
+      <c r="C45" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D45" t="str">
+        <v>执照</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>eventually</v>
+      </c>
+      <c r="B46" t="str">
+        <v>/ɪˈventʃuəli/</v>
+      </c>
+      <c r="C46" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D46" t="str">
+        <v>最终</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>envelope</v>
+      </c>
+      <c r="B47" t="str">
+        <v>/ˈenvələʊp/</v>
+      </c>
+      <c r="C47" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D47" t="str">
+        <v>信封</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>distance</v>
+      </c>
+      <c r="B48" t="str">
+        <v>/ˈdɪstəns/</v>
+      </c>
+      <c r="C48" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D48" t="str">
+        <v>距离</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>as</v>
+      </c>
+      <c r="B49" t="str">
+        <v>/əz,æz/</v>
+      </c>
+      <c r="C49" t="str">
+        <v>v./adv./prep./conj.</v>
+      </c>
+      <c r="D49" t="str">
+        <v>作为</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>agreement</v>
+      </c>
+      <c r="B50" t="str">
+        <v>/əˈɡriːmənt/</v>
+      </c>
+      <c r="C50" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D50" t="str">
+        <v>协议</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>observe</v>
+      </c>
+      <c r="B51" t="str">
+        <v>/əbˈzɜːrv/</v>
+      </c>
+      <c r="C51" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D51" t="str">
         <v>观察</v>
       </c>
-      <c r="D36" t="str">
-        <v>observation(观察)📢</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>shop</v>
-      </c>
-      <c r="C37" t="str">
-        <v>商店</v>
-      </c>
-      <c r="D37" t="str">
-        <v>shop(商店)📢</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>fibre</v>
-      </c>
-      <c r="C38" t="str">
-        <v>纤维</v>
-      </c>
-      <c r="D38" t="str">
-        <v>fibre(纤维)📢</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>rigid</v>
-      </c>
-      <c r="C39" t="str">
-        <v>刻板的</v>
-      </c>
-      <c r="D39" t="str">
-        <v>rigid(刻板的)📢</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>care</v>
-      </c>
-      <c r="C40" t="str">
-        <v>关注</v>
-      </c>
-      <c r="D40" t="str">
-        <v>care(关注)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>drive</v>
-      </c>
-      <c r="C41" t="str">
-        <v>驱动</v>
-      </c>
-      <c r="D41" t="str">
-        <v>drive(驱动)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>northeast</v>
-      </c>
-      <c r="C42" t="str">
-        <v>东北</v>
-      </c>
-      <c r="D42" t="str">
-        <v>northeast(东北)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>stripe</v>
-      </c>
-      <c r="C43" t="str">
-        <v>条纹</v>
-      </c>
-      <c r="D43" t="str">
-        <v>stripe(条纹)📢</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="str">
-        <v>invade</v>
-      </c>
-      <c r="C44" t="str">
-        <v>进入</v>
-      </c>
-      <c r="D44" t="str">
-        <v>invade(进入)📢</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="str">
-        <v>aboard</v>
-      </c>
-      <c r="C45" t="str">
-        <v>在车上</v>
-      </c>
-      <c r="D45" t="str">
-        <v>aboard(在车上)📢</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="str">
-        <v>instance</v>
-      </c>
-      <c r="C46" t="str">
-        <v>例子</v>
-      </c>
-      <c r="D46" t="str">
-        <v>instance(例子)📢</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="str">
-        <v>essential</v>
-      </c>
-      <c r="C47" t="str">
-        <v>本质</v>
-      </c>
-      <c r="D47" t="str">
-        <v>essential(本质)📢</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>care</v>
-      </c>
-      <c r="C48" t="str">
-        <v>关心</v>
-      </c>
-      <c r="D48" t="str">
-        <v>care(关心)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>rigid</v>
-      </c>
-      <c r="C49" t="str">
-        <v>僵硬的</v>
-      </c>
-      <c r="D49" t="str">
-        <v>rigid(僵硬的)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>lavatory</v>
-      </c>
-      <c r="C50" t="str">
-        <v>厕所</v>
-      </c>
-      <c r="D50" t="str">
-        <v>lavatory(厕所)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>dot</v>
-      </c>
-      <c r="C51" t="str">
-        <v>小点</v>
-      </c>
-      <c r="D51" t="str">
-        <v>dot(小点)📢</v>
-      </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>angle</v>
       </c>
       <c r="B52" t="str">
-        <v>license</v>
+        <v>/ˈæŋɡl/</v>
       </c>
       <c r="C52" t="str">
-        <v>执照</v>
+        <v>n./v.</v>
       </c>
       <c r="D52" t="str">
-        <v>license(执照)📢</v>
+        <v>视角</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>everybody</v>
       </c>
       <c r="B53" t="str">
-        <v>Western</v>
+        <v>/ˈevribɑːdi,ˈevribʌdi/</v>
       </c>
       <c r="C53" t="str">
-        <v>西方</v>
+        <v>n./pron.</v>
       </c>
       <c r="D53" t="str">
-        <v>Western(西方)📢</v>
+        <v>每个人</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <v>53</v>
+      <c r="A54" t="str">
+        <v>hazard</v>
       </c>
       <c r="B54" t="str">
-        <v>eventually</v>
+        <v>/ˈhæzərd/</v>
       </c>
       <c r="C54" t="str">
-        <v>最终</v>
+        <v>n./vt.</v>
       </c>
       <c r="D54" t="str">
-        <v>eventually(最终)📢</v>
+        <v>危险</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55">
-        <v>54</v>
+      <c r="A55" t="str">
+        <v>overtake</v>
       </c>
       <c r="B55" t="str">
-        <v>Roman</v>
+        <v>/ˌoʊvərˈteɪk/</v>
       </c>
       <c r="C55" t="str">
-        <v>罗马</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D55" t="str">
-        <v>Roman(罗马)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>envelope</v>
-      </c>
-      <c r="C56" t="str">
-        <v>信封</v>
-      </c>
-      <c r="D56" t="str">
-        <v>envelope(信封)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>distance</v>
-      </c>
-      <c r="C57" t="str">
-        <v>距离</v>
-      </c>
-      <c r="D57" t="str">
-        <v>distance(距离)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>as</v>
-      </c>
-      <c r="C58" t="str">
-        <v>作为</v>
-      </c>
-      <c r="D58" t="str">
-        <v>as(作为)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>reputation</v>
-      </c>
-      <c r="C59" t="str">
-        <v>声誉</v>
-      </c>
-      <c r="D59" t="str">
-        <v>reputation(声誉)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>agreement</v>
-      </c>
-      <c r="C60" t="str">
-        <v>协议</v>
-      </c>
-      <c r="D60" t="str">
-        <v>agreement(协议)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>observe</v>
-      </c>
-      <c r="C61" t="str">
-        <v>观察</v>
-      </c>
-      <c r="D61" t="str">
-        <v>observe(观察)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>angle</v>
-      </c>
-      <c r="C62" t="str">
-        <v>视角</v>
-      </c>
-      <c r="D62" t="str">
-        <v>angle(视角)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>steady</v>
-      </c>
-      <c r="C63" t="str">
-        <v>沉稳</v>
-      </c>
-      <c r="D63" t="str">
-        <v>steady(沉稳)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>everybody</v>
-      </c>
-      <c r="C64" t="str">
-        <v>每个人</v>
-      </c>
-      <c r="D64" t="str">
-        <v>everybody(每个人)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>hazard</v>
-      </c>
-      <c r="C65" t="str">
-        <v>危险</v>
-      </c>
-      <c r="D65" t="str">
-        <v>hazard(危险)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>optimistic</v>
-      </c>
-      <c r="C66" t="str">
-        <v>乐观的</v>
-      </c>
-      <c r="D66" t="str">
-        <v>optimistic(乐观的)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>overtake</v>
-      </c>
-      <c r="C67" t="str">
         <v>超越</v>
-      </c>
-      <c r="D67" t="str">
-        <v>overtake(超越)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>drive</v>
-      </c>
-      <c r="C68" t="str">
-        <v>驱使</v>
-      </c>
-      <c r="D68" t="str">
-        <v>drive(驱使)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>continue</v>
-      </c>
-      <c r="C69" t="str">
-        <v>坚持</v>
-      </c>
-      <c r="D69" t="str">
-        <v>continue(坚持)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>youth</v>
-      </c>
-      <c r="C70" t="str">
-        <v>青春</v>
-      </c>
-      <c r="D70" t="str">
-        <v>youth(青春)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>steady</v>
-      </c>
-      <c r="C71" t="str">
-        <v>稳固地</v>
-      </c>
-      <c r="D71" t="str">
-        <v>steady(稳固地)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D55"/>
   </ignoredErrors>
 </worksheet>
 </file>